--- a/reports/2024-10-23.xlsx
+++ b/reports/2024-10-23.xlsx
@@ -468,10 +468,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.002152574479076976</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.002152574479076976</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
